--- a/artfynd/A 39946-2026 artfynd.xlsx
+++ b/artfynd/A 39946-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759980</v>
       </c>
       <c r="B2" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759979</v>
       </c>
       <c r="B3" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2026 artfynd.xlsx
+++ b/artfynd/A 39946-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759980</v>
       </c>
       <c r="B2" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759979</v>
       </c>
       <c r="B3" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2026 artfynd.xlsx
+++ b/artfynd/A 39946-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759980</v>
       </c>
       <c r="B2" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759979</v>
       </c>
       <c r="B3" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2026 artfynd.xlsx
+++ b/artfynd/A 39946-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136759979</v>
       </c>
       <c r="B3" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2026 artfynd.xlsx
+++ b/artfynd/A 39946-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759980</v>
       </c>
       <c r="B2" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759979</v>
       </c>
       <c r="B3" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2026 artfynd.xlsx
+++ b/artfynd/A 39946-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136759979</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2026 artfynd.xlsx
+++ b/artfynd/A 39946-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759980</v>
       </c>
       <c r="B2" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759979</v>
       </c>
       <c r="B3" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2026 artfynd.xlsx
+++ b/artfynd/A 39946-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759980</v>
       </c>
       <c r="B2" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759979</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2026 artfynd.xlsx
+++ b/artfynd/A 39946-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759980</v>
       </c>
       <c r="B2" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759979</v>
       </c>
       <c r="B3" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2026 artfynd.xlsx
+++ b/artfynd/A 39946-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136759979</v>
       </c>
       <c r="B3" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2026 artfynd.xlsx
+++ b/artfynd/A 39946-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759980</v>
       </c>
       <c r="B2" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759979</v>
       </c>
       <c r="B3" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2026 artfynd.xlsx
+++ b/artfynd/A 39946-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136759979</v>
       </c>
       <c r="B3" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
